--- a/isms-core-framework/A.8-technological-controls/isms-a.8.2-3-5-authentication-privileged-access/WKBK/90_workbooks/ISMS-IMP-A.8.2-3-5.S5_Access_Restrictions_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.2-3-5-authentication-privileged-access/WKBK/90_workbooks/ISMS-IMP-A.8.2-3-5.S5_Access_Restrictions_20260208.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:49</t>
+          <t>08.02.2026 12:26</t>
         </is>
       </c>
     </row>
